--- a/e2e/Test Results/Excel/Automation_Test_Report.xlsx
+++ b/e2e/Test Results/Excel/Automation_Test_Report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
   <si>
     <t>Test Name</t>
   </si>
@@ -25,16 +25,23 @@
     <t>Error</t>
   </si>
   <si>
+    <t>should navigate to Sign Up screen from Login screen</t>
+  </si>
+  <si>
+    <t>failed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unknown error: net::ERR_CONNECTION_REFUSED
+  (Session info: chrome=150.0.7871.116)</t>
+  </si>
+  <si>
     <t>should load the application successfully</t>
   </si>
   <si>
-    <t>passed</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>should verify flutter-view is present (if flutter web)</t>
+  </si>
+  <si>
+    <t>should test login with valid test credentials and reach dashboard</t>
   </si>
 </sst>
 </file>
@@ -411,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -441,7 +448,7 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>6101</v>
+        <v>5286</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
@@ -455,9 +462,37 @@
         <v>5</v>
       </c>
       <c r="C3">
-        <v>272</v>
+        <v>5805</v>
       </c>
       <c r="D3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>2394</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>5299</v>
+      </c>
+      <c r="D5" t="s">
         <v>6</v>
       </c>
     </row>
